--- a/userdata.xlsx
+++ b/userdata.xlsx
@@ -2,32 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Score-Tracker-Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,13 +49,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -422,26 +417,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -450,11 +445,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lester</t>
+          <t>john</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -465,7 +460,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>lester</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -480,15 +475,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">james </t>
+          <t>marian</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>77</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>joshua</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>88</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cris</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>66</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>78</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lester</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>101</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>maricar</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>kaila</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>999</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
         </is>
       </c>
     </row>
